--- a/output/北塩原村_他AIレビューの確認.xlsx
+++ b/output/北塩原村_他AIレビューの確認.xlsx
@@ -782,12 +782,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>障がい児相談支援の令和８年度の実績を確認しています</t>
+          <t>障がい児の台帳の値です</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Ｍ-137⑥で照会済み。18歳到達はＭ-20で照会済み</t>
+          <t>Ｍ-137で照会し、令和８年10月23日に障がい児の台帳を受領した。令和８年度は台帳の値（実人数４人）に改め、令和７年度の資料２－３との食い違いはＭ-141で照会した。18歳到達はＭ-20で照会済み</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_他AIレビューの確認.xlsx
+++ b/output/北塩原村_他AIレビューの確認.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_指摘の検証" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_追加確認とＫＰＩ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_正本の書き換え" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_第2回の検証" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_正本の書き換え" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,6 +1195,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>他ＡＩのレビュー（第２回）の検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>指摘14点を正本・ＫＰＩ定義票の現物に当てた。正しい3点・一部正しい3点・既に対応済み8点。レビューの数値（見込量・実績）は正本と一致した。本文が挙げる添付（ZIP・Word・Excel）は受領していない。基準日：令和8年10月23日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>レビューの指摘（語）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>照合先</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>照合語</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度途中実績は11.7人/月ですが、令和9年度見込量は8人/月</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>一人ずつ積み上げて置き直すかどうかを確認しています</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>前回のR03と同じ。Ｍ-139と注記で照会済み。約12人を基準にする案は村の判断として、Ｍ-139の回答の後に当方で置き直しの案を作る</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>計画相談支援の単位不整合</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>国の基本指針は計画相談支援の見込量を月間の利用者数で示すこととしている</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>前回のR01と同じ（注記とＭ-136）。レビューの言う３つの数え方のうち、月平均利用者数をＫＰＩに足した（Ｋ-27）。モニタリングはＫ-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度は「確定年度実績」ではなく「暫定的な途中実績」</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>一部正しい</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>令和８年度は年度途中の暫定値であり</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>正しい。注記に「暫定値であり通年の実績とは比べられない」と明記した。ただし「推移分析のグラフで令和6～8年度を一本の時系列にしている」点は当たらない。正本の図（Ｚ-1）は令和２〜７年度の給付費であり、令和８年度の途中の値を描いた図は無い</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>居宅介護は2人から4人、5人へ増えます</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>逆に、居宅介護（表５-５）と</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Ｍ-139で照会済み。増える理由（卒業・移行・新規）はＭ-21・Ｍ-15・Ｍ-20の回答で一人ずつ対応させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>R8 22人日/月 → R9 12人日/月</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>表５-８の見込量は月12人日です</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>前回のR06で注記とＭ-139に足した</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ06</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>短期入所 人日/月 | 2 | 2 | 1 | 5 | 5 | 5</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>見込量の月５人日を下回ります</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>新しい指摘で、正しい。実績は月２人日以下で見込量は月５人日。注記（ＤＫ-注３）とＭ-139に足した</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>児童発達支援 人日/月 | 5 | 2 | 3 | 8 | 8 | 8</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>児童お一人ずつの見通しで確認しています</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>新しい指摘で、正しい。児童発達支援の見込量（月８人日）が実績を上回り、保育所等訪問支援は令和８年度に利用があるのに令和９年度が０人、障がい児相談支援は令和８年度の４人から３人に減る。表５-15の見込量の後に注記（ＤＫ-注８）を足し、Ｍ-139に足した</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ08</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>重度障がい者等の内数が未確定</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>表５-９に掲げた重度の障がいのある方の内数</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>前回のR08と同じ。Ｍ-22・Ｍ-26・Ｍ-87で照会済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>「個別避難計画作成件数」は活動・出力</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ＫＰＩ</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>個別避難計画の策定件数</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>正しい。第４次計画の8指標を一律に「成果」としていた。個別に区分し直し、成果3・活動3・体制2とした（トイレの設置率と医療的ケア児の受入れ体制は体制、物品調達・特定健診・個別避難計画は活動）。研修・開催回数・配置は当初から活動・体制に分けていた</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ10</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>村が採否を決める必要があります</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>一部正しい</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ＫＰＩ</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>参考：レビューの目標案</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>提案として受ける。目標値の欄には入れず「参考」の欄に置いた（レビュー自身が国の指定ではないとしている）。新しく提案された6指標（退院支援の方針の作成率、就労継続率、計画相談の月平均、地域生活の選択肢の提示率、乖離の未説明件数、必要量の確保率）をＫ-25〜Ｋ-30として足した</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>4人×6％＝0.24人</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>国の率をそのまま当てると１人未満になる</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>既に書いてある。第１章の県計画との関係の表で、４人に国の率を当てると１人未満になることと、県が国の率を下回る目標を置いた理由が本村にも当てはまることを書き、第４章２（１）で引いている。全員の意向確認はＫ-03・Ｋ-28で見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ12</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>未充足量＝必要量－実利用可能な供給量</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>必要な量と、実際に確保できる量とを分けて把握します</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>既に第５章冒頭に同じ枠組みがある。数への当てはめは事業所への照会（Ｍ-24・Ｍ-25）の回答の後。確保率をＫ-30として足した</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ｂ13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>令和8年告示第4号を確定根拠とし、追加改正案は参考資料</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>こども家庭庁・厚生労働省告示第４号</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>正本と一致する。当方は国の原本を source/基本指針 に持っている</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Ｂ14</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>原票から集計結果までの1件単位の完全再監査はできません</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>一部正しい</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>制約として正しい。原本は利用者ごとの記録のため、レビュー用の一式には入れていない（受領資料つき版には入れた）。集計は抽出スクリプトで原本から再現できる</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/output/北塩原村_他AIレビューの確認.xlsx
+++ b/output/北塩原村_他AIレビューの確認.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_指摘の検証" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_追加確認とＫＰＩ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_第2回の検証" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_正本の書き換え" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_第3回の検証" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_正本の書き換え" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,7 +51,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +88,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -114,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -144,6 +150,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1711,6 +1720,562 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="76" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>他ＡＩのレビュー（第３回）の検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>指摘16点を正本・ＫＰＩ定義票・参考値の現物に当てた。正しい5点・一部正しい1点・既に対応済み5点・村の回答待ち5点。レビューが示した数値と行数は参考値と一致した。基準日：令和8年10月24日</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>レビューの指摘（語）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>照合先</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>照合語</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ01</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>令和9～11年度の正式見込量は未修正</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>村の回答待ち</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>正本の見込量は直していません</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>指摘のとおり未修正であり、意図したもの。見込量は村の判断であり、Ｍ-139の回答を待って参考値を一人ずつの積上げに置き換え、正本に反映する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>月平均6.8人の参考値と注記を追加</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>村の回答待ち</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>正本</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>国の基本指針は計画相談支援の見込量を月間の利用者数で示すこととしている</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>「未解消」の判定は正しい。数え方はＭ-136の回答で決める。決まった数え方を正本の表・注記とＫ-27に同時に当てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ03</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>サービスごとの最終収録月・対象月・利用者数を明示</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>起点の対象月</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>正しい。参考値の表に「起点の対象月」の列を足し、サービスごとに使った実施月と月数を示した（例：共同生活援助 令和８年度 実施月６月〜８月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>人数起点と利用量の対象期間を原則合わせる</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>起点と同じ月で出す</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>正しい。１人当たりの利用量を、起点と同じ直近３か月で出すように改めた。生活介護は109人日から101人日、生活訓練は22人日から21人日、児童発達支援は３人日から４人日に変わった</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>計算内部の小数値と表示丸め後の値を別列で保存</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>表に置く場合</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>既に「参考値」（小数）と「表に置く場合」（整数）を別の列にしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ06</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>少数利用サービスは人数差1人以上を必ず個別確認</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>人数は0.5人未満</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>既に満たしている。人数の判定の幅は0.5人であり、１人以上の差はすべて「離れている」に入る</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ07</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>「需要0」と認定せず最新の支給決定・事業所情報を照会</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Ｍ-137①②で就労移行支援と就労継続支援Ａ型の令和８年度を照会済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ08</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>利用量であり定着成果そのものではない</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>ＫＰＩ</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>６か月・12か月後の就労継続率）と併せて見る</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>正しい。レビューが挙げた9指標の定義を直した。Ｋ-08はＫ-26と併せて見る、Ｋ-13は接続先を保健・保育・学校・医療に広げる、Ｋ-19は予定・実施・延期・中止を定義、Ｋ-21は対象０を「該当なし」、Ｋ-24は全対象と優先対象で分母を分ける、Ｋ-29は乖離の幅の検討案、Ｋ-30は地理的・実質的に利用できる量、Ｋ-32は関連指標と位置づけ、Ｋ-33は分母の固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ09</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>0件の場合の取扱い</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ＫＰＩ</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>該当なし</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>正しい。定義票に「０件・該当なしの扱い」の欄を足し、率の指標は分母が０の年度を「該当なし」とした（17欄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ10</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>当該計算の記載と「0人目標の妥当性の確認」は別</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>村の回答待ち</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>正しい。妥当性は４人の意向（Ｍ-94）で確かめる。Ｋ-03・Ｋ-28で毎年度見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ11</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>第3版ZIP単体では生成器の完全な独立再実行ができない</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>正しい</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>正しい。レビュー用の一式に共通のモジュール（kitashiobara_common.py、build_kitashiobara_shihyou_sokutei.py）を入れていなかった。リポジトリでは再現性点検（全生成器の再実行と内容の照合）で確かめているが、次の一式からは依存するモジュールと実行の手順を同梱する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ12</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>内部の権限者による原票検証と結果の記録が必要</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>一部正しい</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>制約として正しい。原本からの集計は抽出スクリプトで行い、資料２－３との検算（排泄管理支援用具の令和６年度75件の一致など）を自己点検に入れている。原本を見られる村の担当者による確認は、照会への回答の際にお願いする</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ13</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>次の3点を一括更新</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>既に仕組みにしている。参考値とＫＰＩ定義票は正本の表を毎回読み、照会は台帳の一か所から照会文へ読み込むため、村の回答で正本を直せば他は作り直しで揃う</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ14</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>見込量確定後の算定と位置づけ</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>村の回答待ち</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>第１回のR11と同じ。見込量の確定の後に給付費と村負担を出す</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>確認先・照会番号を整理</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>村の回答待ち</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>重度の方の内数はＭ-22・Ｍ-26・Ｍ-87の回答待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Ｃ16</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>正本との差異17行（このうち単位の相違2行を含む）・概ね整合5行</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>既に対応済み</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>参考値</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>数え方が違う</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>レビューの数え方は参考値の表と一致する</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
